--- a/儲槽作業日報/TK604_2026_Temperature_Report_v2.xlsx
+++ b/儲槽作業日報/TK604_2026_Temperature_Report_v2.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="2026_Temperature" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1535,7 +1535,7 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>13</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>23</c:v>
@@ -1637,7 +1637,7 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>14</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>24</c:v>
@@ -4231,7 +4231,7 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>14</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>24</c:v>
@@ -7334,7 +7334,7 @@
         <v>66</v>
       </c>
       <c r="B66">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C66">
         <v>18</v>
@@ -7912,10 +7912,10 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C100">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D100">
         <v>28</v>
